--- a/老虎机数学入门-PartI-计算模型.xlsx
+++ b/老虎机数学入门-PartI-计算模型.xlsx
@@ -8480,6 +8480,9 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:U202" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -17998,5 +18001,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AK126" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>